--- a/S158_122/1.0.0/S-158_122_1_0_0_20260323.xlsx
+++ b/S158_122/1.0.0/S-158_122_1_0_0_20260323.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\git\S-122-Product-Specification-Development\S158_122\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B922F83B-39D8-4687-A39E-E1496417AA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E579598-A112-42A8-BA9D-BBB99532D430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="18240" tabRatio="647" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">S122Checks!$K$1:$K$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">S122Checks!$K$1:$K$63</definedName>
     <definedName name="S101_Disposition">[1]Lists!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1" iterateCount="1000" concurrentCalc="0"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="318">
   <si>
     <t>Document Number</t>
   </si>
@@ -646,9 +646,6 @@
     <t>Correct values of maximum and minimum display scales.</t>
   </si>
   <si>
-    <t>4.4.1</t>
-  </si>
-  <si>
     <t>Dataset contains overlapping DataCoverage features.</t>
   </si>
   <si>
@@ -793,18 +790,6 @@
     <t>Amend fileLocator value</t>
   </si>
   <si>
-    <t>Complex attribute sourceIndication must have at least one sub-attribute populated</t>
-  </si>
-  <si>
-    <t>For each complex attribute sourceIndication with none of its sub-attributes populated</t>
-  </si>
-  <si>
-    <t>Delete or amend sourceIndication</t>
-  </si>
-  <si>
-    <t>various</t>
-  </si>
-  <si>
     <t>Repeated attribute value</t>
   </si>
   <si>
@@ -838,9 +823,6 @@
     <t>[7.4]; [2.6.10]</t>
   </si>
   <si>
-    <t>[12.16]; [5.2.1]</t>
-  </si>
-  <si>
     <t>5.2.1, 17.9, various</t>
   </si>
   <si>
@@ -856,9 +838,6 @@
     <t>11.5.1</t>
   </si>
   <si>
-    <t>[12.16]; [10.4]</t>
-  </si>
-  <si>
     <t>2.4.8.5</t>
   </si>
   <si>
@@ -890,9 +869,6 @@
   </si>
   <si>
     <t>Value required for mandatory attribute</t>
-  </si>
-  <si>
-    <t>For each attribute binding listed in in DCEG clause 2.4 as not nillableAND which is not populated</t>
   </si>
   <si>
     <t>Populate attribute</t>
@@ -1040,6 +1016,27 @@
   </si>
   <si>
     <t>Remarks for information complex attribute from GI registry</t>
+  </si>
+  <si>
+    <t>12.10</t>
+  </si>
+  <si>
+    <t>[12.13]; [5.2.1]</t>
+  </si>
+  <si>
+    <t>[12.13]; [10.4]</t>
+  </si>
+  <si>
+    <t>4.3.2</t>
+  </si>
+  <si>
+    <t>4.3.1</t>
+  </si>
+  <si>
+    <t>12.2.1</t>
+  </si>
+  <si>
+    <t>For each attribute binding listed in in DCEG clause 2.4 as not nillable AND which is not populated</t>
   </si>
 </sst>
 </file>
@@ -1530,7 +1527,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1639,9 +1636,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1654,9 +1648,6 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1676,9 +1667,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1687,8 +1675,62 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1702,66 +1744,50 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="2" builtinId="26"/>
@@ -2070,14 +2096,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="33.6" customHeight="1">
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="82"/>
       <c r="H2" s="32"/>
     </row>
     <row r="3" spans="2:8" s="8" customFormat="1" ht="20.45" customHeight="1">
@@ -2181,7 +2207,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
@@ -2203,7 +2229,7 @@
       <c r="G12" s="33"/>
     </row>
     <row r="13" spans="2:8" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="83" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -2217,7 +2243,7 @@
       <c r="G13" s="33"/>
     </row>
     <row r="14" spans="2:8" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B14" s="68"/>
+      <c r="B14" s="83"/>
       <c r="C14" s="22" t="s">
         <v>77</v>
       </c>
@@ -2229,7 +2255,7 @@
       <c r="G14" s="33"/>
     </row>
     <row r="15" spans="2:8" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B15" s="68"/>
+      <c r="B15" s="83"/>
       <c r="C15" s="23" t="s">
         <v>78</v>
       </c>
@@ -2241,7 +2267,7 @@
       <c r="G15" s="33"/>
     </row>
     <row r="16" spans="2:8" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B16" s="68"/>
+      <c r="B16" s="83"/>
       <c r="C16" s="44" t="s">
         <v>29</v>
       </c>
@@ -2253,7 +2279,7 @@
       <c r="G16" s="33"/>
     </row>
     <row r="17" spans="2:7" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B17" s="68"/>
+      <c r="B17" s="83"/>
       <c r="C17" s="24"/>
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
@@ -2261,7 +2287,7 @@
       <c r="G17" s="33"/>
     </row>
     <row r="18" spans="2:7" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B18" s="68"/>
+      <c r="B18" s="83"/>
       <c r="C18" s="26"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -2296,7 +2322,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="2" customWidth="1"/>
@@ -2305,8 +2331,8 @@
     <col min="4" max="4" width="34.5703125" style="4" customWidth="1"/>
     <col min="5" max="5" width="57.28515625" style="4" customWidth="1"/>
     <col min="6" max="6" width="34.140625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="88" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" style="79" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="90" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.28515625" style="1" customWidth="1"/>
     <col min="11" max="11" width="8.85546875" style="1" customWidth="1"/>
@@ -2335,25 +2361,25 @@
       <c r="F1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="69" t="s">
+      <c r="G1" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="70" t="s">
+      <c r="H1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="71" t="s">
+      <c r="I1" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="72" t="s">
+      <c r="J1" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="72" t="s">
+      <c r="K1" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="73" t="s">
+      <c r="L1" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="M1" s="74" t="s">
+      <c r="M1" s="65" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2368,19 +2394,19 @@
       <c r="C2" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="66" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="76" t="s">
+      <c r="F2" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="48">
+      <c r="H2" s="85">
         <v>7.3</v>
       </c>
       <c r="I2" s="47" t="s">
@@ -2388,7 +2414,7 @@
       </c>
       <c r="J2" s="46"/>
       <c r="K2" s="46"/>
-      <c r="L2" s="63" t="s">
+      <c r="L2" s="60" t="s">
         <v>69</v>
       </c>
       <c r="M2" s="47" t="s">
@@ -2406,19 +2432,19 @@
       <c r="C3" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D3" s="52" t="s">
-        <v>301</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>302</v>
-      </c>
-      <c r="F3" s="49" t="s">
-        <v>303</v>
-      </c>
-      <c r="G3" s="52" t="s">
+      <c r="D3" s="51" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="51" t="s">
+        <v>294</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>295</v>
+      </c>
+      <c r="G3" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="48">
+      <c r="H3" s="85">
         <v>12.8</v>
       </c>
       <c r="I3" s="47" t="s">
@@ -2426,7 +2452,7 @@
       </c>
       <c r="J3" s="46"/>
       <c r="K3" s="46"/>
-      <c r="L3" s="63" t="s">
+      <c r="L3" s="60" t="s">
         <v>71</v>
       </c>
       <c r="M3" s="47" t="s">
@@ -2444,19 +2470,19 @@
       <c r="C4" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D4" s="52" t="s">
-        <v>304</v>
-      </c>
-      <c r="E4" s="52" t="s">
+      <c r="D4" s="51" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="49" t="s">
+      <c r="F4" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="G4" s="52" t="s">
+      <c r="G4" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="48">
+      <c r="H4" s="85">
         <v>4.2</v>
       </c>
       <c r="I4" s="47" t="s">
@@ -2464,7 +2490,7 @@
       </c>
       <c r="J4" s="46"/>
       <c r="K4" s="46"/>
-      <c r="L4" s="63" t="s">
+      <c r="L4" s="60" t="s">
         <v>69</v>
       </c>
       <c r="M4" s="47" t="s">
@@ -2482,19 +2508,19 @@
       <c r="C5" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="52" t="s">
-        <v>235</v>
-      </c>
-      <c r="E5" s="52" t="s">
+      <c r="D5" s="51" t="s">
+        <v>234</v>
+      </c>
+      <c r="E5" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="77" t="s">
+      <c r="F5" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="52" t="s">
+      <c r="G5" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="48">
+      <c r="H5" s="85">
         <v>12.4</v>
       </c>
       <c r="I5" s="47" t="s">
@@ -2502,7 +2528,7 @@
       </c>
       <c r="J5" s="47"/>
       <c r="K5" s="47"/>
-      <c r="L5" s="63" t="s">
+      <c r="L5" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M5" s="47" t="s">
@@ -2520,27 +2546,27 @@
       <c r="C6" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="E6" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="77" t="s">
+      <c r="F6" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="H6" s="53" t="s">
-        <v>226</v>
+      <c r="H6" s="86" t="s">
+        <v>225</v>
       </c>
       <c r="I6" s="47" t="s">
         <v>31</v>
       </c>
       <c r="J6" s="47"/>
       <c r="K6" s="47"/>
-      <c r="L6" s="63" t="s">
+      <c r="L6" s="60" t="s">
         <v>69</v>
       </c>
       <c r="M6" s="47" t="s">
@@ -2558,19 +2584,19 @@
       <c r="C7" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="E7" s="52" t="s">
-        <v>305</v>
-      </c>
-      <c r="F7" s="78" t="s">
+      <c r="E7" s="51" t="s">
+        <v>297</v>
+      </c>
+      <c r="F7" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="48">
+      <c r="H7" s="85">
         <v>12.5</v>
       </c>
       <c r="I7" s="47" t="s">
@@ -2580,7 +2606,7 @@
         <v>26</v>
       </c>
       <c r="K7" s="47"/>
-      <c r="L7" s="63" t="s">
+      <c r="L7" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M7" s="47" t="s">
@@ -2598,19 +2624,19 @@
       <c r="C8" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="E8" s="52" t="s">
-        <v>306</v>
-      </c>
-      <c r="F8" s="79" t="s">
+      <c r="E8" s="51" t="s">
+        <v>298</v>
+      </c>
+      <c r="F8" s="70" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="52" t="s">
+      <c r="G8" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="53" t="s">
+      <c r="H8" s="86" t="s">
         <v>162</v>
       </c>
       <c r="I8" s="47" t="s">
@@ -2620,7 +2646,7 @@
         <v>26</v>
       </c>
       <c r="K8" s="47"/>
-      <c r="L8" s="63" t="s">
+      <c r="L8" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M8" s="47" t="s">
@@ -2638,19 +2664,19 @@
       <c r="C9" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="52" t="s">
+      <c r="E9" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="F9" s="49" t="s">
+      <c r="F9" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="G9" s="52" t="s">
+      <c r="G9" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="H9" s="53"/>
+      <c r="H9" s="86"/>
       <c r="I9" s="47" t="s">
         <v>31</v>
       </c>
@@ -2658,7 +2684,7 @@
         <v>26</v>
       </c>
       <c r="K9" s="47"/>
-      <c r="L9" s="63" t="s">
+      <c r="L9" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M9" s="47" t="s">
@@ -2676,29 +2702,29 @@
       <c r="C10" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="E10" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="49" t="s">
+      <c r="F10" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="52" t="s">
+      <c r="G10" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="H10" s="53"/>
+      <c r="H10" s="86"/>
       <c r="I10" s="47" t="s">
         <v>31</v>
       </c>
       <c r="J10" s="46"/>
       <c r="K10" s="47"/>
-      <c r="L10" s="63" t="s">
+      <c r="L10" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M10" s="47" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="39" thickBot="1">
@@ -2712,19 +2738,19 @@
       <c r="C11" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="52" t="s">
+      <c r="E11" s="51" t="s">
         <v>196</v>
       </c>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="52" t="s">
+      <c r="G11" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="53">
+      <c r="H11" s="86">
         <v>3</v>
       </c>
       <c r="I11" s="47" t="s">
@@ -2732,7 +2758,7 @@
       </c>
       <c r="J11" s="46"/>
       <c r="K11" s="46"/>
-      <c r="L11" s="63" t="s">
+      <c r="L11" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M11" s="47"/>
@@ -2748,19 +2774,19 @@
       <c r="C12" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="51" t="s">
         <v>197</v>
       </c>
-      <c r="F12" s="49" t="s">
+      <c r="F12" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="52" t="s">
+      <c r="G12" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="53">
+      <c r="H12" s="86">
         <v>3</v>
       </c>
       <c r="I12" s="47" t="s">
@@ -2768,7 +2794,7 @@
       </c>
       <c r="J12" s="46"/>
       <c r="K12" s="46"/>
-      <c r="L12" s="63" t="s">
+      <c r="L12" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M12" s="47"/>
@@ -2784,27 +2810,27 @@
       <c r="C13" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D13" s="52" t="s">
+      <c r="D13" s="51" t="s">
+        <v>226</v>
+      </c>
+      <c r="E13" s="66" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" s="48" t="s">
         <v>227</v>
       </c>
-      <c r="E13" s="75" t="s">
-        <v>167</v>
-      </c>
-      <c r="F13" s="49" t="s">
-        <v>228</v>
-      </c>
-      <c r="G13" s="52" t="s">
+      <c r="G13" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="48" t="s">
-        <v>258</v>
+      <c r="H13" s="85" t="s">
+        <v>253</v>
       </c>
       <c r="I13" s="47" t="s">
         <v>31</v>
       </c>
       <c r="J13" s="46"/>
       <c r="K13" s="46"/>
-      <c r="L13" s="63" t="s">
+      <c r="L13" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M13" s="47" t="s">
@@ -2822,27 +2848,27 @@
       <c r="C14" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="D14" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="49" t="s">
         <v>169</v>
       </c>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="H14" s="60" t="s">
-        <v>259</v>
+      <c r="H14" s="87" t="s">
+        <v>254</v>
       </c>
       <c r="I14" s="47" t="s">
         <v>31</v>
       </c>
       <c r="J14" s="46"/>
       <c r="K14" s="46"/>
-      <c r="L14" s="63" t="s">
+      <c r="L14" s="60" t="s">
         <v>69</v>
       </c>
       <c r="M14" s="47" t="s">
@@ -2860,19 +2886,19 @@
       <c r="C15" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="51" t="s">
+        <v>228</v>
+      </c>
+      <c r="E15" s="51" t="s">
         <v>229</v>
       </c>
-      <c r="E15" s="52" t="s">
+      <c r="F15" s="48" t="s">
         <v>230</v>
       </c>
-      <c r="F15" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="G15" s="52" t="s">
+      <c r="G15" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="48">
+      <c r="H15" s="85">
         <v>12.9</v>
       </c>
       <c r="I15" s="47" t="s">
@@ -2880,7 +2906,7 @@
       </c>
       <c r="J15" s="46"/>
       <c r="K15" s="46"/>
-      <c r="L15" s="63" t="s">
+      <c r="L15" s="60" t="s">
         <v>69</v>
       </c>
       <c r="M15" s="47" t="s">
@@ -2898,27 +2924,27 @@
       <c r="C16" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D16" s="52" t="s">
+      <c r="D16" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="E16" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="49" t="s">
+      <c r="F16" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="G16" s="75" t="s">
+      <c r="G16" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="48">
-        <v>12.1</v>
+      <c r="H16" s="85" t="s">
+        <v>311</v>
       </c>
       <c r="I16" s="47" t="s">
         <v>31</v>
       </c>
       <c r="J16" s="46"/>
       <c r="K16" s="46"/>
-      <c r="L16" s="63" t="s">
+      <c r="L16" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M16" s="47" t="s">
@@ -2933,34 +2959,34 @@
         <f t="shared" si="0"/>
         <v>122_0016</v>
       </c>
-      <c r="C17" s="80" t="s">
+      <c r="C17" s="71" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="81" t="s">
+      <c r="D17" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="52" t="s">
+      <c r="E17" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="49" t="s">
+      <c r="F17" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="G17" s="61" t="s">
+      <c r="G17" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="H17" s="60" t="s">
-        <v>260</v>
+      <c r="H17" s="87" t="s">
+        <v>255</v>
       </c>
       <c r="I17" s="47" t="s">
         <v>31</v>
       </c>
       <c r="J17" s="46"/>
       <c r="K17" s="46"/>
-      <c r="L17" s="63" t="s">
+      <c r="L17" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M17" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="26.25" thickBot="1">
@@ -2974,20 +3000,20 @@
       <c r="C18" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D18" s="82" t="s">
+      <c r="D18" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="52" t="s">
-        <v>307</v>
-      </c>
-      <c r="F18" s="51" t="s">
+      <c r="E18" s="51" t="s">
+        <v>299</v>
+      </c>
+      <c r="F18" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="62" t="s">
+      <c r="G18" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="58" t="s">
-        <v>261</v>
+      <c r="H18" s="89" t="s">
+        <v>256</v>
       </c>
       <c r="I18" s="46" t="s">
         <v>31</v>
@@ -2996,7 +3022,7 @@
         <v>26</v>
       </c>
       <c r="K18" s="47"/>
-      <c r="L18" s="63" t="s">
+      <c r="L18" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M18" s="47" t="s">
@@ -3014,27 +3040,27 @@
       <c r="C19" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D19" s="82" t="s">
+      <c r="D19" s="73" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="52" t="s">
-        <v>308</v>
-      </c>
-      <c r="F19" s="51" t="s">
+      <c r="E19" s="51" t="s">
+        <v>300</v>
+      </c>
+      <c r="F19" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="63" t="s">
+      <c r="G19" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="H19" s="58" t="s">
-        <v>262</v>
+      <c r="H19" s="89" t="s">
+        <v>257</v>
       </c>
       <c r="I19" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J19" s="46"/>
       <c r="K19" s="47"/>
-      <c r="L19" s="63" t="s">
+      <c r="L19" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M19" s="47"/>
@@ -3050,27 +3076,27 @@
       <c r="C20" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D20" s="75" t="s">
+      <c r="D20" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="F20" s="51" t="s">
+      <c r="E20" s="51" t="s">
+        <v>235</v>
+      </c>
+      <c r="F20" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="52" t="s">
+      <c r="G20" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H20" s="64" t="s">
-        <v>263</v>
+      <c r="H20" s="88" t="s">
+        <v>258</v>
       </c>
       <c r="I20" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J20" s="46"/>
       <c r="K20" s="47"/>
-      <c r="L20" s="63" t="s">
+      <c r="L20" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M20" s="47"/>
@@ -3086,19 +3112,19 @@
       <c r="C21" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D21" s="75" t="s">
+      <c r="D21" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="52" t="s">
+      <c r="E21" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="51" t="s">
+      <c r="F21" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="G21" s="52" t="s">
+      <c r="G21" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="48">
+      <c r="H21" s="85">
         <v>13.1</v>
       </c>
       <c r="I21" s="46" t="s">
@@ -3106,7 +3132,7 @@
       </c>
       <c r="J21" s="46"/>
       <c r="K21" s="46"/>
-      <c r="L21" s="63" t="s">
+      <c r="L21" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M21" s="47"/>
@@ -3122,19 +3148,19 @@
       <c r="C22" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D22" s="83" t="s">
+      <c r="D22" s="74" t="s">
         <v>104</v>
       </c>
-      <c r="E22" s="83" t="s">
+      <c r="E22" s="74" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="84" t="s">
+      <c r="F22" s="75" t="s">
         <v>116</v>
       </c>
-      <c r="G22" s="83" t="s">
+      <c r="G22" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="H22" s="48">
+      <c r="H22" s="85">
         <v>13.1</v>
       </c>
       <c r="I22" s="46" t="s">
@@ -3142,7 +3168,7 @@
       </c>
       <c r="J22" s="46"/>
       <c r="K22" s="46"/>
-      <c r="L22" s="63" t="s">
+      <c r="L22" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M22" s="47"/>
@@ -3155,22 +3181,22 @@
         <f t="shared" si="0"/>
         <v>122_0022</v>
       </c>
-      <c r="C23" s="55" t="s">
+      <c r="C23" s="53" t="s">
         <v>185</v>
       </c>
-      <c r="D23" s="56" t="s">
-        <v>233</v>
-      </c>
-      <c r="E23" s="56" t="s">
-        <v>309</v>
-      </c>
-      <c r="F23" s="56" t="s">
+      <c r="D23" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="E23" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="F23" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="G23" s="57" t="s">
+      <c r="G23" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="48">
+      <c r="H23" s="85">
         <v>14.1</v>
       </c>
       <c r="I23" s="46" t="s">
@@ -3180,11 +3206,11 @@
         <v>26</v>
       </c>
       <c r="K23" s="46"/>
-      <c r="L23" s="63" t="s">
+      <c r="L23" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M23" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="26.25" thickBot="1">
@@ -3198,27 +3224,27 @@
       <c r="C24" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D24" s="52" t="s">
+      <c r="D24" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="52" t="s">
+      <c r="E24" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="85" t="s">
+      <c r="F24" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="G24" s="63" t="s">
+      <c r="G24" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="H24" s="60" t="s">
-        <v>264</v>
+      <c r="H24" s="87" t="s">
+        <v>259</v>
       </c>
       <c r="I24" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J24" s="46"/>
       <c r="K24" s="46"/>
-      <c r="L24" s="63" t="s">
+      <c r="L24" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M24" s="47" t="s">
@@ -3236,27 +3262,27 @@
       <c r="C25" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D25" s="52" t="s">
-        <v>310</v>
-      </c>
-      <c r="E25" s="52" t="s">
-        <v>311</v>
-      </c>
-      <c r="F25" s="51" t="s">
+      <c r="D25" s="51" t="s">
+        <v>302</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>303</v>
+      </c>
+      <c r="F25" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="62" t="s">
+      <c r="G25" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="H25" s="58" t="s">
-        <v>260</v>
+      <c r="H25" s="89" t="s">
+        <v>255</v>
       </c>
       <c r="I25" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J25" s="46"/>
       <c r="K25" s="46"/>
-      <c r="L25" s="63" t="s">
+      <c r="L25" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M25" s="47"/>
@@ -3272,27 +3298,27 @@
       <c r="C26" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D26" s="52" t="s">
+      <c r="D26" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="E26" s="52" t="s">
+      <c r="E26" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="F26" s="51" t="s">
+      <c r="F26" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="G26" s="63" t="s">
+      <c r="G26" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="H26" s="60" t="s">
-        <v>265</v>
+      <c r="H26" s="87" t="s">
+        <v>312</v>
       </c>
       <c r="I26" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J26" s="46"/>
       <c r="K26" s="46"/>
-      <c r="L26" s="86" t="s">
+      <c r="L26" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M26" s="47"/>
@@ -3308,25 +3334,25 @@
       <c r="C27" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D27" s="52" t="s">
+      <c r="D27" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="52" t="s">
+      <c r="E27" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="51" t="s">
+      <c r="F27" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="G27" s="52" t="s">
+      <c r="G27" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="H27" s="64"/>
+      <c r="H27" s="88"/>
       <c r="I27" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J27" s="46"/>
       <c r="K27" s="46"/>
-      <c r="L27" s="86" t="s">
+      <c r="L27" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M27" s="47"/>
@@ -3342,19 +3368,19 @@
       <c r="C28" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D28" s="52" t="s">
+      <c r="D28" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="52" t="s">
+      <c r="E28" s="51" t="s">
         <v>90</v>
       </c>
-      <c r="F28" s="51" t="s">
+      <c r="F28" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="G28" s="52" t="s">
+      <c r="G28" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H28" s="53" t="s">
+      <c r="H28" s="86" t="s">
         <v>174</v>
       </c>
       <c r="I28" s="46" t="s">
@@ -3362,11 +3388,11 @@
       </c>
       <c r="J28" s="46"/>
       <c r="K28" s="46"/>
-      <c r="L28" s="86" t="s">
+      <c r="L28" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M28" s="47" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="39" thickBot="1">
@@ -3380,31 +3406,31 @@
       <c r="C29" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="D29" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="52" t="s">
+      <c r="E29" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="F29" s="51" t="s">
+      <c r="F29" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="G29" s="52" t="s">
+      <c r="G29" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H29" s="64" t="s">
-        <v>266</v>
+      <c r="H29" s="88" t="s">
+        <v>260</v>
       </c>
       <c r="I29" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J29" s="46"/>
       <c r="K29" s="46"/>
-      <c r="L29" s="86" t="s">
+      <c r="L29" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M29" s="47" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="51.75" thickBot="1">
@@ -3418,31 +3444,31 @@
       <c r="C30" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D30" s="52" t="s">
+      <c r="D30" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="52" t="s">
+      <c r="E30" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="F30" s="51" t="s">
+      <c r="F30" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="G30" s="52" t="s">
+      <c r="G30" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H30" s="64" t="s">
-        <v>267</v>
+      <c r="H30" s="88" t="s">
+        <v>261</v>
       </c>
       <c r="I30" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J30" s="46"/>
       <c r="K30" s="46"/>
-      <c r="L30" s="86" t="s">
+      <c r="L30" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M30" s="47" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="26.25" thickBot="1">
@@ -3456,19 +3482,19 @@
       <c r="C31" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D31" s="52" t="s">
+      <c r="D31" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="52" t="s">
+      <c r="E31" s="51" t="s">
         <v>93</v>
       </c>
-      <c r="F31" s="51" t="s">
+      <c r="F31" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="G31" s="52" t="s">
+      <c r="G31" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="53" t="s">
+      <c r="H31" s="86" t="s">
         <v>179</v>
       </c>
       <c r="I31" s="46" t="s">
@@ -3476,7 +3502,7 @@
       </c>
       <c r="J31" s="46"/>
       <c r="K31" s="47"/>
-      <c r="L31" s="86" t="s">
+      <c r="L31" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M31" s="47"/>
@@ -3492,27 +3518,27 @@
       <c r="C32" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D32" s="52" t="s">
+      <c r="D32" s="51" t="s">
         <v>108</v>
       </c>
-      <c r="E32" s="52" t="s">
+      <c r="E32" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F32" s="51" t="s">
+      <c r="F32" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="G32" s="52" t="s">
+      <c r="G32" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H32" s="64" t="s">
-        <v>269</v>
+      <c r="H32" s="88" t="s">
+        <v>263</v>
       </c>
       <c r="I32" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J32" s="46"/>
       <c r="K32" s="46"/>
-      <c r="L32" s="86" t="s">
+      <c r="L32" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M32" s="47"/>
@@ -3528,27 +3554,27 @@
       <c r="C33" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D33" s="52" t="s">
+      <c r="D33" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="E33" s="52" t="s">
+      <c r="E33" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="F33" s="51" t="s">
+      <c r="F33" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="G33" s="52" t="s">
+      <c r="G33" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H33" s="53" t="s">
-        <v>270</v>
+      <c r="H33" s="86" t="s">
+        <v>264</v>
       </c>
       <c r="I33" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J33" s="46"/>
       <c r="K33" s="46"/>
-      <c r="L33" s="86" t="s">
+      <c r="L33" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M33" s="47"/>
@@ -3564,19 +3590,19 @@
       <c r="C34" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D34" s="52" t="s">
+      <c r="D34" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="E34" s="52" t="s">
+      <c r="E34" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="F34" s="51" t="s">
+      <c r="F34" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="G34" s="52" t="s">
+      <c r="G34" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H34" s="64">
+      <c r="H34" s="88">
         <v>10.6</v>
       </c>
       <c r="I34" s="46" t="s">
@@ -3584,7 +3610,7 @@
       </c>
       <c r="J34" s="46"/>
       <c r="K34" s="46"/>
-      <c r="L34" s="86" t="s">
+      <c r="L34" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M34" s="47"/>
@@ -3600,27 +3626,27 @@
       <c r="C35" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D35" s="52" t="s">
+      <c r="D35" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="52" t="s">
+      <c r="E35" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="F35" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="G35" s="52" t="s">
+      <c r="G35" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="H35" s="64" t="s">
-        <v>271</v>
+      <c r="H35" s="88" t="s">
+        <v>313</v>
       </c>
       <c r="I35" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J35" s="46"/>
       <c r="K35" s="46"/>
-      <c r="L35" s="86" t="s">
+      <c r="L35" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M35" s="47"/>
@@ -3636,19 +3662,19 @@
       <c r="C36" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D36" s="52" t="s">
+      <c r="D36" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="52" t="s">
+      <c r="E36" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="F36" s="51" t="s">
+      <c r="F36" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="G36" s="52" t="s">
+      <c r="G36" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H36" s="64" t="s">
+      <c r="H36" s="88" t="s">
         <v>175</v>
       </c>
       <c r="I36" s="46" t="s">
@@ -3656,7 +3682,7 @@
       </c>
       <c r="J36" s="46"/>
       <c r="K36" s="46"/>
-      <c r="L36" s="86" t="s">
+      <c r="L36" s="77" t="s">
         <v>69</v>
       </c>
       <c r="M36" s="47"/>
@@ -3672,19 +3698,19 @@
       <c r="C37" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D37" s="75" t="s">
+      <c r="D37" s="66" t="s">
         <v>109</v>
       </c>
-      <c r="E37" s="75" t="s">
+      <c r="E37" s="66" t="s">
         <v>176</v>
       </c>
-      <c r="F37" s="51" t="s">
+      <c r="F37" s="50" t="s">
         <v>177</v>
       </c>
-      <c r="G37" s="52" t="s">
+      <c r="G37" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H37" s="64">
+      <c r="H37" s="88">
         <v>12.11</v>
       </c>
       <c r="I37" s="46" t="s">
@@ -3694,7 +3720,7 @@
         <v>26</v>
       </c>
       <c r="K37" s="47"/>
-      <c r="L37" s="86" t="s">
+      <c r="L37" s="77" t="s">
         <v>161</v>
       </c>
       <c r="M37" s="47" t="s">
@@ -3712,19 +3738,19 @@
       <c r="C38" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D38" s="52" t="s">
+      <c r="D38" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="E38" s="52" t="s">
-        <v>312</v>
-      </c>
-      <c r="F38" s="51" t="s">
-        <v>313</v>
-      </c>
-      <c r="G38" s="52" t="s">
+      <c r="E38" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="F38" s="50" t="s">
+        <v>305</v>
+      </c>
+      <c r="G38" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H38" s="53">
+      <c r="H38" s="86">
         <v>7.5</v>
       </c>
       <c r="I38" s="46" t="s">
@@ -3734,7 +3760,7 @@
         <v>26</v>
       </c>
       <c r="K38" s="47"/>
-      <c r="L38" s="86" t="s">
+      <c r="L38" s="77" t="s">
         <v>161</v>
       </c>
       <c r="M38" s="47" t="s">
@@ -3753,19 +3779,19 @@
       <c r="C39" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="52" t="s">
+      <c r="D39" s="51" t="s">
         <v>184</v>
       </c>
-      <c r="E39" s="52" t="s">
+      <c r="E39" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="F39" s="51" t="s">
+      <c r="F39" s="50" t="s">
         <v>186</v>
       </c>
-      <c r="G39" s="52" t="s">
+      <c r="G39" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H39" s="53">
+      <c r="H39" s="86">
         <v>7.3</v>
       </c>
       <c r="I39" s="46" t="s">
@@ -3773,7 +3799,7 @@
       </c>
       <c r="J39" s="46"/>
       <c r="K39" s="47"/>
-      <c r="L39" s="86" t="s">
+      <c r="L39" s="77" t="s">
         <v>187</v>
       </c>
       <c r="M39" s="47"/>
@@ -3790,34 +3816,34 @@
       <c r="C40" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="52" t="s">
+      <c r="D40" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="E40" s="52" t="s">
+      <c r="E40" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="F40" s="49" t="s">
+      <c r="F40" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="G40" s="52" t="s">
+      <c r="G40" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H40" s="53" t="s">
-        <v>201</v>
+      <c r="H40" s="86" t="s">
+        <v>314</v>
       </c>
       <c r="I40" s="47" t="s">
         <v>26</v>
       </c>
       <c r="J40" s="46"/>
       <c r="K40" s="46"/>
-      <c r="L40" s="63" t="s">
+      <c r="L40" s="60" t="s">
         <v>187</v>
       </c>
       <c r="M40" s="47"/>
     </row>
     <row r="41" spans="1:13" ht="26.25" thickBot="1">
       <c r="A41" s="41" t="str">
-        <f t="shared" ref="A41:A62" si="1">_xlfn.CONCAT("122_ED2_",TEXT(ROW()-ROW(A$39)+1,"000"))</f>
+        <f t="shared" ref="A41:A61" si="1">_xlfn.CONCAT("122_ED2_",TEXT(ROW()-ROW(A$39)+1,"000"))</f>
         <v>122_ED2_003</v>
       </c>
       <c r="B41" s="42" t="str">
@@ -3827,27 +3853,27 @@
       <c r="C41" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D41" s="52" t="s">
+      <c r="D41" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="E41" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="E41" s="52" t="s">
+      <c r="F41" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="F41" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G41" s="52" t="s">
+      <c r="G41" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H41" s="53" t="s">
-        <v>201</v>
+      <c r="H41" s="86" t="s">
+        <v>315</v>
       </c>
       <c r="I41" s="47" t="s">
         <v>26</v>
       </c>
       <c r="J41" s="46"/>
       <c r="K41" s="46"/>
-      <c r="L41" s="63" t="s">
+      <c r="L41" s="60" t="s">
         <v>187</v>
       </c>
       <c r="M41" s="47"/>
@@ -3858,33 +3884,33 @@
         <v>122_ED2_004</v>
       </c>
       <c r="B42" s="42" t="str">
-        <f t="shared" ref="B42:B62" si="2">_xlfn.CONCAT("122_", TEXT(ROW()-1, "0000"))</f>
+        <f t="shared" ref="B42:B61" si="2">_xlfn.CONCAT("122_", TEXT(ROW()-1, "0000"))</f>
         <v>122_0041</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D42" s="52" t="s">
+      <c r="D42" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" s="51" t="s">
         <v>205</v>
       </c>
-      <c r="E42" s="52" t="s">
+      <c r="F42" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="F42" s="49" t="s">
-        <v>207</v>
-      </c>
-      <c r="G42" s="52" t="s">
+      <c r="G42" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H42" s="53" t="s">
-        <v>201</v>
+      <c r="H42" s="86" t="s">
+        <v>315</v>
       </c>
       <c r="I42" s="47" t="s">
         <v>26</v>
       </c>
       <c r="J42" s="46"/>
       <c r="K42" s="46"/>
-      <c r="L42" s="63" t="s">
+      <c r="L42" s="60" t="s">
         <v>187</v>
       </c>
       <c r="M42" s="47"/>
@@ -3901,23 +3927,25 @@
       <c r="C43" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D43" s="52" t="s">
+      <c r="D43" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>306</v>
+      </c>
+      <c r="F43" s="48" t="s">
         <v>208</v>
       </c>
-      <c r="E43" s="52" t="s">
-        <v>314</v>
-      </c>
-      <c r="F43" s="49" t="s">
-        <v>209</v>
-      </c>
-      <c r="G43" s="52"/>
-      <c r="H43" s="53"/>
+      <c r="G43" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="H43" s="86"/>
       <c r="I43" s="47" t="s">
         <v>26</v>
       </c>
       <c r="J43" s="46"/>
       <c r="K43" s="46"/>
-      <c r="L43" s="63" t="s">
+      <c r="L43" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M43" s="47"/>
@@ -3934,27 +3962,27 @@
       <c r="C44" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D44" s="52" t="s">
+      <c r="D44" s="51" t="s">
+        <v>209</v>
+      </c>
+      <c r="E44" s="51" t="s">
         <v>210</v>
       </c>
-      <c r="E44" s="52" t="s">
+      <c r="F44" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="F44" s="49" t="s">
+      <c r="G44" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="H44" s="86" t="s">
         <v>212</v>
-      </c>
-      <c r="G44" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="H44" s="53" t="s">
-        <v>213</v>
       </c>
       <c r="I44" s="47" t="s">
         <v>26</v>
       </c>
       <c r="J44" s="46"/>
       <c r="K44" s="46"/>
-      <c r="L44" s="63" t="s">
+      <c r="L44" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M44" s="47"/>
@@ -3971,27 +3999,27 @@
       <c r="C45" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D45" s="54" t="s">
+      <c r="D45" s="52" t="s">
+        <v>213</v>
+      </c>
+      <c r="E45" s="51" t="s">
         <v>214</v>
       </c>
-      <c r="E45" s="52" t="s">
+      <c r="F45" s="48" t="s">
         <v>215</v>
       </c>
-      <c r="F45" s="49" t="s">
-        <v>216</v>
-      </c>
-      <c r="G45" s="52" t="s">
+      <c r="G45" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H45" s="53" t="s">
-        <v>272</v>
+      <c r="H45" s="86" t="s">
+        <v>265</v>
       </c>
       <c r="I45" s="47" t="s">
         <v>31</v>
       </c>
       <c r="J45" s="46"/>
       <c r="K45" s="46"/>
-      <c r="L45" s="63" t="s">
+      <c r="L45" s="60" t="s">
         <v>70</v>
       </c>
       <c r="M45" s="47"/>
@@ -4008,27 +4036,27 @@
       <c r="C46" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D46" s="52" t="s">
+      <c r="D46" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="E46" s="51" t="s">
         <v>217</v>
       </c>
-      <c r="E46" s="52" t="s">
+      <c r="F46" s="50" t="s">
         <v>218</v>
       </c>
-      <c r="F46" s="51" t="s">
-        <v>219</v>
-      </c>
-      <c r="G46" s="52" t="s">
+      <c r="G46" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H46" s="53">
-        <v>12.1</v>
+      <c r="H46" s="86" t="s">
+        <v>316</v>
       </c>
       <c r="I46" s="46" t="s">
         <v>31</v>
       </c>
       <c r="J46" s="46"/>
       <c r="K46" s="46"/>
-      <c r="L46" s="86" t="s">
+      <c r="L46" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M46" s="47"/>
@@ -4045,19 +4073,19 @@
       <c r="C47" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D47" s="52" t="s">
+      <c r="D47" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="E47" s="51" t="s">
         <v>220</v>
       </c>
-      <c r="E47" s="52" t="s">
-        <v>221</v>
-      </c>
-      <c r="F47" s="51" t="s">
-        <v>219</v>
-      </c>
-      <c r="G47" s="52" t="s">
+      <c r="F47" s="50" t="s">
+        <v>218</v>
+      </c>
+      <c r="G47" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H47" s="53">
+      <c r="H47" s="86">
         <v>12.1</v>
       </c>
       <c r="I47" s="46" t="s">
@@ -4065,7 +4093,7 @@
       </c>
       <c r="J47" s="46"/>
       <c r="K47" s="46"/>
-      <c r="L47" s="86" t="s">
+      <c r="L47" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M47" s="47"/>
@@ -4082,20 +4110,20 @@
       <c r="C48" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D48" s="52" t="s">
+      <c r="D48" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="E48" s="51" t="s">
+        <v>307</v>
+      </c>
+      <c r="F48" s="50" t="s">
         <v>222</v>
       </c>
-      <c r="E48" s="52" t="s">
-        <v>315</v>
-      </c>
-      <c r="F48" s="51" t="s">
+      <c r="G48" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="H48" s="86" t="s">
         <v>223</v>
-      </c>
-      <c r="G48" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="H48" s="53" t="s">
-        <v>224</v>
       </c>
       <c r="I48" s="46" t="s">
         <v>31</v>
@@ -4104,14 +4132,14 @@
         <v>26</v>
       </c>
       <c r="K48" s="46"/>
-      <c r="L48" s="86" t="s">
+      <c r="L48" s="77" t="s">
         <v>70</v>
       </c>
       <c r="M48" s="47" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="39" thickBot="1">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="39" thickBot="1">
       <c r="A49" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_011</v>
@@ -4123,28 +4151,28 @@
       <c r="C49" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D49" s="75" t="s">
+      <c r="D49" s="66" t="s">
         <v>180</v>
       </c>
-      <c r="E49" s="52" t="s">
+      <c r="E49" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="F49" s="51" t="s">
+      <c r="F49" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="G49" s="52" t="s">
+      <c r="G49" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H49" s="48">
+      <c r="H49" s="85">
         <v>13.1</v>
       </c>
       <c r="I49" s="46"/>
       <c r="J49" s="46"/>
       <c r="K49" s="46"/>
-      <c r="L49" s="86"/>
+      <c r="L49" s="77"/>
       <c r="M49" s="47"/>
     </row>
-    <row r="50" spans="1:13" ht="39" thickBot="1">
+    <row r="50" spans="1:14" ht="39" thickBot="1">
       <c r="A50" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_012</v>
@@ -4153,23 +4181,23 @@
         <f t="shared" si="2"/>
         <v>122_0049</v>
       </c>
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="56" t="s">
         <v>168</v>
       </c>
       <c r="D50" s="47" t="s">
+        <v>236</v>
+      </c>
+      <c r="E50" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="E50" s="47" t="s">
+      <c r="F50" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="F50" s="47" t="s">
+      <c r="G50" s="57" t="s">
+        <v>25</v>
+      </c>
+      <c r="H50" s="89" t="s">
         <v>239</v>
-      </c>
-      <c r="G50" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="H50" s="58" t="s">
-        <v>240</v>
       </c>
       <c r="I50" s="46" t="s">
         <v>26</v>
@@ -4181,7 +4209,7 @@
       </c>
       <c r="M50" s="47"/>
     </row>
-    <row r="51" spans="1:13" ht="26.25" thickBot="1">
+    <row r="51" spans="1:14" ht="26.25" thickBot="1">
       <c r="A51" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_013</v>
@@ -4190,22 +4218,22 @@
         <f t="shared" si="2"/>
         <v>122_0050</v>
       </c>
-      <c r="C51" s="58" t="s">
+      <c r="C51" s="56" t="s">
         <v>189</v>
       </c>
       <c r="D51" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="E51" s="47" t="s">
         <v>241</v>
       </c>
-      <c r="E51" s="47" t="s">
+      <c r="F51" s="47" t="s">
         <v>242</v>
       </c>
-      <c r="F51" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="G51" s="59" t="s">
+      <c r="G51" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="H51" s="58">
+      <c r="H51" s="89">
         <v>7.3</v>
       </c>
       <c r="I51" s="46" t="s">
@@ -4218,7 +4246,7 @@
       </c>
       <c r="M51" s="47"/>
     </row>
-    <row r="52" spans="1:13" ht="26.25" thickBot="1">
+    <row r="52" spans="1:14" ht="26.25" thickBot="1">
       <c r="A52" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_014</v>
@@ -4227,23 +4255,23 @@
         <f t="shared" si="2"/>
         <v>122_0051</v>
       </c>
-      <c r="C52" s="58" t="s">
+      <c r="C52" s="56" t="s">
         <v>189</v>
       </c>
       <c r="D52" s="47" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E52" s="47" t="s">
+        <v>243</v>
+      </c>
+      <c r="F52" s="47" t="s">
         <v>244</v>
       </c>
-      <c r="F52" s="47" t="s">
-        <v>245</v>
-      </c>
-      <c r="G52" s="59" t="s">
+      <c r="G52" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="H52" s="58" t="s">
-        <v>213</v>
+      <c r="H52" s="89" t="s">
+        <v>212</v>
       </c>
       <c r="I52" s="46" t="s">
         <v>26</v>
@@ -4251,11 +4279,11 @@
       <c r="J52" s="46"/>
       <c r="K52" s="46"/>
       <c r="L52" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M52" s="47"/>
     </row>
-    <row r="53" spans="1:13" ht="26.25" thickBot="1">
+    <row r="53" spans="1:14" ht="26.25" thickBot="1">
       <c r="A53" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_015</v>
@@ -4264,23 +4292,23 @@
         <f t="shared" si="2"/>
         <v>122_0052</v>
       </c>
-      <c r="C53" s="58" t="s">
+      <c r="C53" s="56" t="s">
         <v>168</v>
       </c>
       <c r="D53" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="E53" s="47" t="s">
         <v>247</v>
       </c>
-      <c r="E53" s="47" t="s">
+      <c r="F53" s="47" t="s">
         <v>248</v>
       </c>
-      <c r="F53" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="G53" s="59" t="s">
+      <c r="G53" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="H53" s="58" t="s">
-        <v>213</v>
+      <c r="H53" s="89" t="s">
+        <v>212</v>
       </c>
       <c r="I53" s="46" t="s">
         <v>26</v>
@@ -4288,83 +4316,85 @@
       <c r="J53" s="46"/>
       <c r="K53" s="46"/>
       <c r="L53" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M53" s="47"/>
     </row>
-    <row r="54" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A54" s="41" t="str">
+    <row r="54" spans="1:14" s="99" customFormat="1" ht="39" thickBot="1">
+      <c r="A54" s="91" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_016</v>
       </c>
-      <c r="B54" s="42" t="str">
+      <c r="B54" s="92" t="str">
         <f t="shared" si="2"/>
         <v>122_0053</v>
       </c>
-      <c r="C54" s="58" t="s">
+      <c r="C54" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="D54" s="47" t="s">
+      <c r="D54" s="94" t="s">
+        <v>249</v>
+      </c>
+      <c r="E54" s="94" t="s">
         <v>250</v>
       </c>
-      <c r="E54" s="47" t="s">
+      <c r="F54" s="94" t="s">
         <v>251</v>
       </c>
-      <c r="F54" s="47" t="s">
+      <c r="G54" s="95" t="s">
+        <v>166</v>
+      </c>
+      <c r="H54" s="96"/>
+      <c r="I54" s="97" t="s">
+        <v>26</v>
+      </c>
+      <c r="J54" s="97"/>
+      <c r="K54" s="97"/>
+      <c r="L54" s="94" t="s">
         <v>252</v>
       </c>
-      <c r="G54" s="59" t="s">
-        <v>68</v>
-      </c>
-      <c r="H54" s="58" t="s">
-        <v>253</v>
-      </c>
-      <c r="I54" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="J54" s="46"/>
-      <c r="K54" s="46"/>
-      <c r="L54" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="M54" s="47"/>
-    </row>
-    <row r="55" spans="1:13" ht="39" thickBot="1">
-      <c r="A55" s="41" t="str">
+      <c r="M54" s="94"/>
+      <c r="N54" s="98"/>
+    </row>
+    <row r="55" spans="1:14" s="99" customFormat="1" ht="39" thickBot="1">
+      <c r="A55" s="91" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_017</v>
       </c>
-      <c r="B55" s="42" t="str">
+      <c r="B55" s="92" t="str">
         <f t="shared" si="2"/>
         <v>122_0054</v>
       </c>
-      <c r="C55" s="58" t="s">
+      <c r="C55" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="D55" s="47" t="s">
-        <v>254</v>
-      </c>
-      <c r="E55" s="47" t="s">
-        <v>255</v>
-      </c>
-      <c r="F55" s="47" t="s">
-        <v>256</v>
-      </c>
-      <c r="G55" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="H55" s="58"/>
-      <c r="I55" s="46" t="s">
+      <c r="D55" s="94" t="s">
+        <v>267</v>
+      </c>
+      <c r="E55" s="94" t="s">
+        <v>268</v>
+      </c>
+      <c r="F55" s="94" t="s">
+        <v>269</v>
+      </c>
+      <c r="G55" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="H55" s="96" t="s">
+        <v>270</v>
+      </c>
+      <c r="I55" s="97" t="s">
         <v>26</v>
       </c>
-      <c r="J55" s="46"/>
-      <c r="K55" s="46"/>
-      <c r="L55" s="47" t="s">
-        <v>257</v>
-      </c>
-      <c r="M55" s="47"/>
-    </row>
-    <row r="56" spans="1:13" ht="39" thickBot="1">
+      <c r="J55" s="97"/>
+      <c r="K55" s="97"/>
+      <c r="L55" s="94" t="s">
+        <v>245</v>
+      </c>
+      <c r="M55" s="94"/>
+      <c r="N55" s="98"/>
+    </row>
+    <row r="56" spans="1:14" ht="26.25" thickBot="1">
       <c r="A56" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_018</v>
@@ -4373,35 +4403,35 @@
         <f t="shared" si="2"/>
         <v>122_0055</v>
       </c>
-      <c r="C56" s="58" t="s">
+      <c r="C56" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D56" s="47" t="s">
+      <c r="D56" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E56" s="72" t="s">
+        <v>271</v>
+      </c>
+      <c r="F56" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="G56" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="H56" s="88" t="s">
         <v>274</v>
-      </c>
-      <c r="E56" s="47" t="s">
-        <v>275</v>
-      </c>
-      <c r="F56" s="47" t="s">
-        <v>276</v>
-      </c>
-      <c r="G56" s="59" t="s">
-        <v>68</v>
-      </c>
-      <c r="H56" s="58" t="s">
-        <v>277</v>
       </c>
       <c r="I56" s="46" t="s">
         <v>26</v>
       </c>
       <c r="J56" s="46"/>
       <c r="K56" s="46"/>
-      <c r="L56" s="47" t="s">
-        <v>246</v>
+      <c r="L56" s="77" t="s">
+        <v>245</v>
       </c>
       <c r="M56" s="47"/>
     </row>
-    <row r="57" spans="1:13" ht="26.25" thickBot="1">
+    <row r="57" spans="1:14" ht="26.25" thickBot="1">
       <c r="A57" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_019</v>
@@ -4411,34 +4441,34 @@
         <v>122_0056</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="E57" s="81" t="s">
-        <v>278</v>
-      </c>
-      <c r="F57" s="51" t="s">
-        <v>280</v>
-      </c>
-      <c r="G57" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="D57" s="72" t="s">
+        <v>275</v>
+      </c>
+      <c r="E57" s="51" t="s">
+        <v>317</v>
+      </c>
+      <c r="F57" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="G57" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H57" s="64" t="s">
-        <v>281</v>
+      <c r="H57" s="88">
+        <v>2.4</v>
       </c>
       <c r="I57" s="46" t="s">
         <v>26</v>
       </c>
       <c r="J57" s="46"/>
       <c r="K57" s="46"/>
-      <c r="L57" s="86" t="s">
-        <v>246</v>
+      <c r="L57" s="77" t="s">
+        <v>245</v>
       </c>
       <c r="M57" s="47"/>
     </row>
-    <row r="58" spans="1:13" ht="26.25" thickBot="1">
+    <row r="58" spans="1:14" ht="39" thickBot="1">
       <c r="A58" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_020</v>
@@ -4450,32 +4480,32 @@
       <c r="C58" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D58" s="81" t="s">
-        <v>282</v>
-      </c>
-      <c r="E58" s="52" t="s">
-        <v>283</v>
-      </c>
-      <c r="F58" s="51" t="s">
-        <v>284</v>
-      </c>
-      <c r="G58" s="52" t="s">
+      <c r="D58" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="E58" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="F58" s="47" t="s">
+        <v>279</v>
+      </c>
+      <c r="G58" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="H58" s="64">
-        <v>2.4</v>
+      <c r="H58" s="89" t="s">
+        <v>280</v>
       </c>
       <c r="I58" s="46" t="s">
         <v>26</v>
       </c>
       <c r="J58" s="46"/>
       <c r="K58" s="46"/>
-      <c r="L58" s="86" t="s">
-        <v>246</v>
+      <c r="L58" s="47" t="s">
+        <v>245</v>
       </c>
       <c r="M58" s="47"/>
     </row>
-    <row r="59" spans="1:13" ht="39" thickBot="1">
+    <row r="59" spans="1:14" ht="39" thickBot="1">
       <c r="A59" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_021</v>
@@ -4485,22 +4515,22 @@
         <v>122_0058</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="D59" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="E59" s="56" t="s">
-        <v>286</v>
+        <v>281</v>
+      </c>
+      <c r="E59" s="54" t="s">
+        <v>282</v>
       </c>
       <c r="F59" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="G59" s="62" t="s">
+        <v>283</v>
+      </c>
+      <c r="G59" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="H59" s="58" t="s">
-        <v>288</v>
+      <c r="H59" s="89" t="s">
+        <v>284</v>
       </c>
       <c r="I59" s="46" t="s">
         <v>26</v>
@@ -4508,11 +4538,11 @@
       <c r="J59" s="46"/>
       <c r="K59" s="46"/>
       <c r="L59" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M59" s="47"/>
     </row>
-    <row r="60" spans="1:13" ht="39" thickBot="1">
+    <row r="60" spans="1:14" ht="26.25" thickBot="1">
       <c r="A60" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_022</v>
@@ -4521,35 +4551,33 @@
         <f t="shared" si="2"/>
         <v>122_0059</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>168</v>
+      <c r="C60" s="56" t="s">
+        <v>189</v>
       </c>
       <c r="D60" s="47" t="s">
-        <v>289</v>
-      </c>
-      <c r="E60" s="56" t="s">
-        <v>290</v>
+        <v>286</v>
+      </c>
+      <c r="E60" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="F60" s="47" t="s">
-        <v>291</v>
-      </c>
-      <c r="G60" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="H60" s="58" t="s">
-        <v>292</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="G60" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="H60" s="89"/>
       <c r="I60" s="46" t="s">
         <v>26</v>
       </c>
       <c r="J60" s="46"/>
       <c r="K60" s="46"/>
       <c r="L60" s="47" t="s">
-        <v>246</v>
+        <v>289</v>
       </c>
       <c r="M60" s="47"/>
     </row>
-    <row r="61" spans="1:13" ht="26.25" thickBot="1">
+    <row r="61" spans="1:14" ht="26.25" thickBot="1">
       <c r="A61" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_023</v>
@@ -4558,83 +4586,48 @@
         <f t="shared" si="2"/>
         <v>122_0060</v>
       </c>
-      <c r="C61" s="58" t="s">
-        <v>189</v>
+      <c r="C61" s="56" t="s">
+        <v>168</v>
       </c>
       <c r="D61" s="47" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E61" s="47" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F61" s="47" t="s">
-        <v>296</v>
-      </c>
-      <c r="G61" s="59" t="s">
+        <v>292</v>
+      </c>
+      <c r="G61" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="H61" s="58"/>
+      <c r="H61" s="89"/>
       <c r="I61" s="46" t="s">
         <v>26</v>
       </c>
       <c r="J61" s="46"/>
       <c r="K61" s="46"/>
       <c r="L61" s="47" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="M61" s="47"/>
     </row>
-    <row r="62" spans="1:13" ht="26.25" thickBot="1">
-      <c r="A62" s="41" t="str">
-        <f t="shared" si="1"/>
-        <v>122_ED2_024</v>
-      </c>
-      <c r="B62" s="42" t="str">
-        <f t="shared" si="2"/>
-        <v>122_0061</v>
-      </c>
-      <c r="C62" s="58" t="s">
-        <v>168</v>
-      </c>
-      <c r="D62" s="47" t="s">
-        <v>298</v>
-      </c>
-      <c r="E62" s="47" t="s">
-        <v>299</v>
-      </c>
-      <c r="F62" s="47" t="s">
-        <v>300</v>
-      </c>
-      <c r="G62" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="H62" s="58"/>
-      <c r="I62" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="J62" s="46"/>
-      <c r="K62" s="46"/>
-      <c r="L62" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="M62" s="47"/>
-    </row>
-    <row r="63" spans="1:13">
+    <row r="62" spans="1:14">
+      <c r="A62" s="41"/>
+      <c r="B62" s="42"/>
+      <c r="C62" s="6"/>
+      <c r="F62" s="78"/>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" s="41"/>
       <c r="B63" s="42"/>
       <c r="C63" s="6"/>
-      <c r="F63" s="87"/>
-    </row>
-    <row r="64" spans="1:13">
-      <c r="A64" s="41"/>
-      <c r="B64" s="42"/>
-      <c r="C64" s="6"/>
-      <c r="F64" s="87"/>
+      <c r="F63" s="78"/>
     </row>
   </sheetData>
-  <autoFilter ref="K1:K64" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="K1:K63" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C64" xr:uid="{1FB138CC-14EF-4406-9E7B-EC5039F9ECE1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C63" xr:uid="{1FB138CC-14EF-4406-9E7B-EC5039F9ECE1}">
       <formula1>"C,E,W"</formula1>
     </dataValidation>
   </dataValidations>

--- a/S158_122/1.0.0/S-158_122_1_0_0_20260323.xlsx
+++ b/S158_122/1.0.0/S-158_122_1_0_0_20260323.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\git\S-122-Product-Specification-Development\S158_122\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E579598-A112-42A8-BA9D-BBB99532D430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4898AD-298B-4365-A0BF-3294727D115E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="18240" tabRatio="647" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1527,7 +1527,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1732,6 +1732,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1744,50 +1765,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="2" builtinId="26"/>
@@ -2096,14 +2073,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="33.6" customHeight="1">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="82"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
       <c r="H2" s="32"/>
     </row>
     <row r="3" spans="2:8" s="8" customFormat="1" ht="20.45" customHeight="1">
@@ -2229,7 +2206,7 @@
       <c r="G12" s="33"/>
     </row>
     <row r="13" spans="2:8" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="90" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -2243,7 +2220,7 @@
       <c r="G13" s="33"/>
     </row>
     <row r="14" spans="2:8" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B14" s="83"/>
+      <c r="B14" s="90"/>
       <c r="C14" s="22" t="s">
         <v>77</v>
       </c>
@@ -2255,7 +2232,7 @@
       <c r="G14" s="33"/>
     </row>
     <row r="15" spans="2:8" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B15" s="83"/>
+      <c r="B15" s="90"/>
       <c r="C15" s="23" t="s">
         <v>78</v>
       </c>
@@ -2267,7 +2244,7 @@
       <c r="G15" s="33"/>
     </row>
     <row r="16" spans="2:8" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B16" s="83"/>
+      <c r="B16" s="90"/>
       <c r="C16" s="44" t="s">
         <v>29</v>
       </c>
@@ -2279,7 +2256,7 @@
       <c r="G16" s="33"/>
     </row>
     <row r="17" spans="2:7" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B17" s="83"/>
+      <c r="B17" s="90"/>
       <c r="C17" s="24"/>
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
@@ -2287,7 +2264,7 @@
       <c r="G17" s="33"/>
     </row>
     <row r="18" spans="2:7" s="8" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B18" s="83"/>
+      <c r="B18" s="90"/>
       <c r="C18" s="26"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -2332,7 +2309,7 @@
     <col min="5" max="5" width="57.28515625" style="4" customWidth="1"/>
     <col min="6" max="6" width="34.140625" style="4" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" style="79" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="90" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="86" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.28515625" style="1" customWidth="1"/>
     <col min="11" max="11" width="8.85546875" style="1" customWidth="1"/>
@@ -2364,7 +2341,7 @@
       <c r="G1" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="84" t="s">
+      <c r="H1" s="80" t="s">
         <v>21</v>
       </c>
       <c r="I1" s="62" t="s">
@@ -2406,7 +2383,7 @@
       <c r="G2" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="85">
+      <c r="H2" s="81">
         <v>7.3</v>
       </c>
       <c r="I2" s="47" t="s">
@@ -2444,7 +2421,7 @@
       <c r="G3" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="85">
+      <c r="H3" s="81">
         <v>12.8</v>
       </c>
       <c r="I3" s="47" t="s">
@@ -2482,7 +2459,7 @@
       <c r="G4" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="85">
+      <c r="H4" s="81">
         <v>4.2</v>
       </c>
       <c r="I4" s="47" t="s">
@@ -2520,7 +2497,7 @@
       <c r="G5" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="85">
+      <c r="H5" s="81">
         <v>12.4</v>
       </c>
       <c r="I5" s="47" t="s">
@@ -2558,7 +2535,7 @@
       <c r="G6" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="H6" s="86" t="s">
+      <c r="H6" s="82" t="s">
         <v>225</v>
       </c>
       <c r="I6" s="47" t="s">
@@ -2596,7 +2573,7 @@
       <c r="G7" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="85">
+      <c r="H7" s="81">
         <v>12.5</v>
       </c>
       <c r="I7" s="47" t="s">
@@ -2636,7 +2613,7 @@
       <c r="G8" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="86" t="s">
+      <c r="H8" s="82" t="s">
         <v>162</v>
       </c>
       <c r="I8" s="47" t="s">
@@ -2676,7 +2653,7 @@
       <c r="G9" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="H9" s="86"/>
+      <c r="H9" s="82"/>
       <c r="I9" s="47" t="s">
         <v>31</v>
       </c>
@@ -2714,7 +2691,7 @@
       <c r="G10" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="H10" s="86"/>
+      <c r="H10" s="82"/>
       <c r="I10" s="47" t="s">
         <v>31</v>
       </c>
@@ -2750,7 +2727,7 @@
       <c r="G11" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="86">
+      <c r="H11" s="82">
         <v>3</v>
       </c>
       <c r="I11" s="47" t="s">
@@ -2786,7 +2763,7 @@
       <c r="G12" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="86">
+      <c r="H12" s="82">
         <v>3</v>
       </c>
       <c r="I12" s="47" t="s">
@@ -2822,7 +2799,7 @@
       <c r="G13" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="85" t="s">
+      <c r="H13" s="81" t="s">
         <v>253</v>
       </c>
       <c r="I13" s="47" t="s">
@@ -2860,7 +2837,7 @@
       <c r="G14" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="H14" s="87" t="s">
+      <c r="H14" s="83" t="s">
         <v>254</v>
       </c>
       <c r="I14" s="47" t="s">
@@ -2898,7 +2875,7 @@
       <c r="G15" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="85">
+      <c r="H15" s="81">
         <v>12.9</v>
       </c>
       <c r="I15" s="47" t="s">
@@ -2936,7 +2913,7 @@
       <c r="G16" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="85" t="s">
+      <c r="H16" s="81" t="s">
         <v>311</v>
       </c>
       <c r="I16" s="47" t="s">
@@ -2974,7 +2951,7 @@
       <c r="G17" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="H17" s="87" t="s">
+      <c r="H17" s="83" t="s">
         <v>255</v>
       </c>
       <c r="I17" s="47" t="s">
@@ -3012,7 +2989,7 @@
       <c r="G18" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="89" t="s">
+      <c r="H18" s="85" t="s">
         <v>256</v>
       </c>
       <c r="I18" s="46" t="s">
@@ -3052,7 +3029,7 @@
       <c r="G19" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="H19" s="89" t="s">
+      <c r="H19" s="85" t="s">
         <v>257</v>
       </c>
       <c r="I19" s="46" t="s">
@@ -3088,7 +3065,7 @@
       <c r="G20" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H20" s="88" t="s">
+      <c r="H20" s="84" t="s">
         <v>258</v>
       </c>
       <c r="I20" s="46" t="s">
@@ -3124,7 +3101,7 @@
       <c r="G21" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="85">
+      <c r="H21" s="81">
         <v>13.1</v>
       </c>
       <c r="I21" s="46" t="s">
@@ -3160,7 +3137,7 @@
       <c r="G22" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="H22" s="85">
+      <c r="H22" s="81">
         <v>13.1</v>
       </c>
       <c r="I22" s="46" t="s">
@@ -3196,7 +3173,7 @@
       <c r="G23" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="85">
+      <c r="H23" s="81">
         <v>14.1</v>
       </c>
       <c r="I23" s="46" t="s">
@@ -3236,7 +3213,7 @@
       <c r="G24" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="H24" s="87" t="s">
+      <c r="H24" s="83" t="s">
         <v>259</v>
       </c>
       <c r="I24" s="46" t="s">
@@ -3274,7 +3251,7 @@
       <c r="G25" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="H25" s="89" t="s">
+      <c r="H25" s="85" t="s">
         <v>255</v>
       </c>
       <c r="I25" s="46" t="s">
@@ -3310,7 +3287,7 @@
       <c r="G26" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="H26" s="87" t="s">
+      <c r="H26" s="83" t="s">
         <v>312</v>
       </c>
       <c r="I26" s="46" t="s">
@@ -3346,7 +3323,7 @@
       <c r="G27" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="H27" s="88"/>
+      <c r="H27" s="84"/>
       <c r="I27" s="46" t="s">
         <v>31</v>
       </c>
@@ -3380,7 +3357,7 @@
       <c r="G28" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H28" s="86" t="s">
+      <c r="H28" s="82" t="s">
         <v>174</v>
       </c>
       <c r="I28" s="46" t="s">
@@ -3418,7 +3395,7 @@
       <c r="G29" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H29" s="88" t="s">
+      <c r="H29" s="84" t="s">
         <v>260</v>
       </c>
       <c r="I29" s="46" t="s">
@@ -3456,7 +3433,7 @@
       <c r="G30" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H30" s="88" t="s">
+      <c r="H30" s="84" t="s">
         <v>261</v>
       </c>
       <c r="I30" s="46" t="s">
@@ -3494,7 +3471,7 @@
       <c r="G31" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="86" t="s">
+      <c r="H31" s="82" t="s">
         <v>179</v>
       </c>
       <c r="I31" s="46" t="s">
@@ -3530,7 +3507,7 @@
       <c r="G32" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H32" s="88" t="s">
+      <c r="H32" s="84" t="s">
         <v>263</v>
       </c>
       <c r="I32" s="46" t="s">
@@ -3566,7 +3543,7 @@
       <c r="G33" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H33" s="86" t="s">
+      <c r="H33" s="82" t="s">
         <v>264</v>
       </c>
       <c r="I33" s="46" t="s">
@@ -3602,7 +3579,7 @@
       <c r="G34" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H34" s="88">
+      <c r="H34" s="84">
         <v>10.6</v>
       </c>
       <c r="I34" s="46" t="s">
@@ -3638,7 +3615,7 @@
       <c r="G35" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="H35" s="88" t="s">
+      <c r="H35" s="84" t="s">
         <v>313</v>
       </c>
       <c r="I35" s="46" t="s">
@@ -3674,7 +3651,7 @@
       <c r="G36" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H36" s="88" t="s">
+      <c r="H36" s="84" t="s">
         <v>175</v>
       </c>
       <c r="I36" s="46" t="s">
@@ -3710,7 +3687,7 @@
       <c r="G37" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H37" s="88">
+      <c r="H37" s="84">
         <v>12.11</v>
       </c>
       <c r="I37" s="46" t="s">
@@ -3750,7 +3727,7 @@
       <c r="G38" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H38" s="86">
+      <c r="H38" s="82">
         <v>7.5</v>
       </c>
       <c r="I38" s="46" t="s">
@@ -3791,7 +3768,7 @@
       <c r="G39" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H39" s="86">
+      <c r="H39" s="82">
         <v>7.3</v>
       </c>
       <c r="I39" s="46" t="s">
@@ -3828,7 +3805,7 @@
       <c r="G40" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H40" s="86" t="s">
+      <c r="H40" s="82" t="s">
         <v>314</v>
       </c>
       <c r="I40" s="47" t="s">
@@ -3865,7 +3842,7 @@
       <c r="G41" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H41" s="86" t="s">
+      <c r="H41" s="82" t="s">
         <v>315</v>
       </c>
       <c r="I41" s="47" t="s">
@@ -3902,7 +3879,7 @@
       <c r="G42" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H42" s="86" t="s">
+      <c r="H42" s="82" t="s">
         <v>315</v>
       </c>
       <c r="I42" s="47" t="s">
@@ -3939,7 +3916,7 @@
       <c r="G43" s="51" t="s">
         <v>166</v>
       </c>
-      <c r="H43" s="86"/>
+      <c r="H43" s="82"/>
       <c r="I43" s="47" t="s">
         <v>26</v>
       </c>
@@ -3974,7 +3951,7 @@
       <c r="G44" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H44" s="86" t="s">
+      <c r="H44" s="82" t="s">
         <v>212</v>
       </c>
       <c r="I44" s="47" t="s">
@@ -4011,7 +3988,7 @@
       <c r="G45" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H45" s="86" t="s">
+      <c r="H45" s="82" t="s">
         <v>265</v>
       </c>
       <c r="I45" s="47" t="s">
@@ -4048,7 +4025,7 @@
       <c r="G46" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H46" s="86" t="s">
+      <c r="H46" s="82" t="s">
         <v>316</v>
       </c>
       <c r="I46" s="46" t="s">
@@ -4085,7 +4062,7 @@
       <c r="G47" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H47" s="86">
+      <c r="H47" s="82">
         <v>12.1</v>
       </c>
       <c r="I47" s="46" t="s">
@@ -4122,7 +4099,7 @@
       <c r="G48" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H48" s="86" t="s">
+      <c r="H48" s="82" t="s">
         <v>223</v>
       </c>
       <c r="I48" s="46" t="s">
@@ -4139,7 +4116,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="39" thickBot="1">
+    <row r="49" spans="1:13" ht="39" thickBot="1">
       <c r="A49" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_011</v>
@@ -4163,7 +4140,7 @@
       <c r="G49" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="H49" s="85">
+      <c r="H49" s="81">
         <v>13.1</v>
       </c>
       <c r="I49" s="46"/>
@@ -4172,7 +4149,7 @@
       <c r="L49" s="77"/>
       <c r="M49" s="47"/>
     </row>
-    <row r="50" spans="1:14" ht="39" thickBot="1">
+    <row r="50" spans="1:13" ht="39" thickBot="1">
       <c r="A50" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_012</v>
@@ -4196,7 +4173,7 @@
       <c r="G50" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="H50" s="89" t="s">
+      <c r="H50" s="85" t="s">
         <v>239</v>
       </c>
       <c r="I50" s="46" t="s">
@@ -4209,7 +4186,7 @@
       </c>
       <c r="M50" s="47"/>
     </row>
-    <row r="51" spans="1:14" ht="26.25" thickBot="1">
+    <row r="51" spans="1:13" ht="26.25" thickBot="1">
       <c r="A51" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_013</v>
@@ -4233,7 +4210,7 @@
       <c r="G51" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="H51" s="89">
+      <c r="H51" s="85">
         <v>7.3</v>
       </c>
       <c r="I51" s="46" t="s">
@@ -4246,7 +4223,7 @@
       </c>
       <c r="M51" s="47"/>
     </row>
-    <row r="52" spans="1:14" ht="26.25" thickBot="1">
+    <row r="52" spans="1:13" ht="26.25" thickBot="1">
       <c r="A52" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_014</v>
@@ -4270,7 +4247,7 @@
       <c r="G52" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="H52" s="89" t="s">
+      <c r="H52" s="85" t="s">
         <v>212</v>
       </c>
       <c r="I52" s="46" t="s">
@@ -4283,7 +4260,7 @@
       </c>
       <c r="M52" s="47"/>
     </row>
-    <row r="53" spans="1:14" ht="26.25" thickBot="1">
+    <row r="53" spans="1:13" ht="26.25" thickBot="1">
       <c r="A53" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_015</v>
@@ -4307,7 +4284,7 @@
       <c r="G53" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="H53" s="89" t="s">
+      <c r="H53" s="85" t="s">
         <v>212</v>
       </c>
       <c r="I53" s="46" t="s">
@@ -4320,81 +4297,79 @@
       </c>
       <c r="M53" s="47"/>
     </row>
-    <row r="54" spans="1:14" s="99" customFormat="1" ht="39" thickBot="1">
-      <c r="A54" s="91" t="str">
+    <row r="54" spans="1:13" ht="39" thickBot="1">
+      <c r="A54" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_016</v>
       </c>
-      <c r="B54" s="92" t="str">
+      <c r="B54" s="42" t="str">
         <f t="shared" si="2"/>
         <v>122_0053</v>
       </c>
-      <c r="C54" s="93" t="s">
+      <c r="C54" s="56" t="s">
         <v>168</v>
       </c>
-      <c r="D54" s="94" t="s">
+      <c r="D54" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="E54" s="94" t="s">
+      <c r="E54" s="47" t="s">
         <v>250</v>
       </c>
-      <c r="F54" s="94" t="s">
+      <c r="F54" s="47" t="s">
         <v>251</v>
       </c>
-      <c r="G54" s="95" t="s">
+      <c r="G54" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="H54" s="96"/>
-      <c r="I54" s="97" t="s">
+      <c r="H54" s="85"/>
+      <c r="I54" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="J54" s="97"/>
-      <c r="K54" s="97"/>
-      <c r="L54" s="94" t="s">
+      <c r="J54" s="46"/>
+      <c r="K54" s="46"/>
+      <c r="L54" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="M54" s="94"/>
-      <c r="N54" s="98"/>
-    </row>
-    <row r="55" spans="1:14" s="99" customFormat="1" ht="39" thickBot="1">
-      <c r="A55" s="91" t="str">
+      <c r="M54" s="47"/>
+    </row>
+    <row r="55" spans="1:13" ht="39" thickBot="1">
+      <c r="A55" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_017</v>
       </c>
-      <c r="B55" s="92" t="str">
+      <c r="B55" s="42" t="str">
         <f t="shared" si="2"/>
         <v>122_0054</v>
       </c>
-      <c r="C55" s="93" t="s">
+      <c r="C55" s="56" t="s">
         <v>168</v>
       </c>
-      <c r="D55" s="94" t="s">
+      <c r="D55" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="E55" s="94" t="s">
+      <c r="E55" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="F55" s="94" t="s">
+      <c r="F55" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="G55" s="95" t="s">
+      <c r="G55" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="H55" s="96" t="s">
+      <c r="H55" s="85" t="s">
         <v>270</v>
       </c>
-      <c r="I55" s="97" t="s">
+      <c r="I55" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="J55" s="97"/>
-      <c r="K55" s="97"/>
-      <c r="L55" s="94" t="s">
+      <c r="J55" s="46"/>
+      <c r="K55" s="46"/>
+      <c r="L55" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="M55" s="94"/>
-      <c r="N55" s="98"/>
-    </row>
-    <row r="56" spans="1:14" ht="26.25" thickBot="1">
+      <c r="M55" s="47"/>
+    </row>
+    <row r="56" spans="1:13" ht="26.25" thickBot="1">
       <c r="A56" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_018</v>
@@ -4418,7 +4393,7 @@
       <c r="G56" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H56" s="88" t="s">
+      <c r="H56" s="84" t="s">
         <v>274</v>
       </c>
       <c r="I56" s="46" t="s">
@@ -4431,7 +4406,7 @@
       </c>
       <c r="M56" s="47"/>
     </row>
-    <row r="57" spans="1:14" ht="26.25" thickBot="1">
+    <row r="57" spans="1:13" ht="26.25" thickBot="1">
       <c r="A57" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_019</v>
@@ -4455,7 +4430,7 @@
       <c r="G57" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="H57" s="88">
+      <c r="H57" s="84">
         <v>2.4</v>
       </c>
       <c r="I57" s="46" t="s">
@@ -4468,7 +4443,7 @@
       </c>
       <c r="M57" s="47"/>
     </row>
-    <row r="58" spans="1:14" ht="39" thickBot="1">
+    <row r="58" spans="1:13" ht="39" thickBot="1">
       <c r="A58" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_020</v>
@@ -4492,7 +4467,7 @@
       <c r="G58" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="H58" s="89" t="s">
+      <c r="H58" s="85" t="s">
         <v>280</v>
       </c>
       <c r="I58" s="46" t="s">
@@ -4505,7 +4480,7 @@
       </c>
       <c r="M58" s="47"/>
     </row>
-    <row r="59" spans="1:14" ht="39" thickBot="1">
+    <row r="59" spans="1:13" ht="39" thickBot="1">
       <c r="A59" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_021</v>
@@ -4529,7 +4504,7 @@
       <c r="G59" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="H59" s="89" t="s">
+      <c r="H59" s="85" t="s">
         <v>284</v>
       </c>
       <c r="I59" s="46" t="s">
@@ -4542,7 +4517,7 @@
       </c>
       <c r="M59" s="47"/>
     </row>
-    <row r="60" spans="1:14" ht="26.25" thickBot="1">
+    <row r="60" spans="1:13" ht="26.25" thickBot="1">
       <c r="A60" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_022</v>
@@ -4566,7 +4541,7 @@
       <c r="G60" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="H60" s="89"/>
+      <c r="H60" s="85"/>
       <c r="I60" s="46" t="s">
         <v>26</v>
       </c>
@@ -4577,7 +4552,7 @@
       </c>
       <c r="M60" s="47"/>
     </row>
-    <row r="61" spans="1:14" ht="26.25" thickBot="1">
+    <row r="61" spans="1:13" ht="26.25" thickBot="1">
       <c r="A61" s="41" t="str">
         <f t="shared" si="1"/>
         <v>122_ED2_023</v>
@@ -4601,7 +4576,7 @@
       <c r="G61" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="H61" s="89"/>
+      <c r="H61" s="85"/>
       <c r="I61" s="46" t="s">
         <v>26</v>
       </c>
@@ -4612,13 +4587,13 @@
       </c>
       <c r="M61" s="47"/>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:13">
       <c r="A62" s="41"/>
       <c r="B62" s="42"/>
       <c r="C62" s="6"/>
       <c r="F62" s="78"/>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:13">
       <c r="A63" s="41"/>
       <c r="B63" s="42"/>
       <c r="C63" s="6"/>

--- a/S158_122/1.0.0/S-158_122_1_0_0_20260323.xlsx
+++ b/S158_122/1.0.0/S-158_122_1_0_0_20260323.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\git\S-122-Product-Specification-Development\S158_122\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4898AD-298B-4365-A0BF-3294727D115E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B9FF0A-A124-49E5-9CED-8840635E3EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="18240" tabRatio="647" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="319">
   <si>
     <t>Document Number</t>
   </si>
@@ -1037,6 +1037,9 @@
   </si>
   <si>
     <t>For each attribute binding listed in in DCEG clause 2.4 as not nillable AND which is not populated</t>
+  </si>
+  <si>
+    <t>2.4.4</t>
   </si>
 </sst>
 </file>
@@ -4539,9 +4542,11 @@
         <v>288</v>
       </c>
       <c r="G60" s="57" t="s">
-        <v>166</v>
-      </c>
-      <c r="H60" s="85"/>
+        <v>68</v>
+      </c>
+      <c r="H60" s="85" t="s">
+        <v>318</v>
+      </c>
       <c r="I60" s="46" t="s">
         <v>26</v>
       </c>
@@ -4574,9 +4579,11 @@
         <v>292</v>
       </c>
       <c r="G61" s="57" t="s">
-        <v>166</v>
-      </c>
-      <c r="H61" s="85"/>
+        <v>68</v>
+      </c>
+      <c r="H61" s="85" t="s">
+        <v>318</v>
+      </c>
       <c r="I61" s="46" t="s">
         <v>26</v>
       </c>
